--- a/Отчёты/ivan-melehin.github.io_2026-09-21_image-audit.xlsx
+++ b/Отчёты/ivan-melehin.github.io_2026-09-21_image-audit.xlsx
@@ -425,7 +425,7 @@
         <v>Время выполнения</v>
       </c>
       <c r="B3" t="str">
-        <v>0 ч. 1 мин. 34 сек.</v>
+        <v>0 ч. 0 мин. 5 сек.</v>
       </c>
     </row>
     <row r="5">

--- a/Отчёты/ivan-melehin.github.io_2026-09-21_image-audit.xlsx
+++ b/Отчёты/ivan-melehin.github.io_2026-09-21_image-audit.xlsx
@@ -425,7 +425,7 @@
         <v>Время выполнения</v>
       </c>
       <c r="B3" t="str">
-        <v>0 ч. 0 мин. 5 сек.</v>
+        <v>0 ч. 0 мин. 9 сек.</v>
       </c>
     </row>
     <row r="5">
